--- a/scripts/tracebility-form-generate.xlsx
+++ b/scripts/tracebility-form-generate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKING\FREELANCER\YEN\SwifletHome\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBDE5E3-8394-496D-A975-D19FAE96766B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A65FD92-331D-4CA3-B7F9-2AD59EAD53B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EC9FEC76-F761-4AE5-9131-399AA55896AB}"/>
   </bookViews>
@@ -172,15 +172,6 @@
     <t>checkbox</t>
   </si>
   <si>
-    <t xml:space="preserve"> {"options": [
-                { "value":"Nhà yến", "label": "Nhà yến", "sortOrder": 1 },
-                { "value":"Sơ chế", "label": "Sơ chế", "sortOrder": 2 },
-                { "value":  "Chế biến", "label": "Chế biến", "sortOrder": 3 },
-                { "value": "Đóng gói", "label": "Đóng gói", "sortOrder": 4 } ],
-               { "value": "Phân phối", "label": "Phân phối", "sortOrder": 5 } ]
-}</t>
-  </si>
-  <si>
     <t>{  "placeholder": "21.028, 105.804",  "regex": "^[-+]?\\d+(\\.\\d+)?,\\s*[-+]?\\d+(\\.\\d+)?$" }</t>
   </si>
   <si>
@@ -369,19 +360,21 @@
   <si>
     <t>{"accept": [".png", ".jpg", ".jpeg"]}</t>
   </si>
+  <si>
+    <t xml:space="preserve"> {"options": [
+                { "value":"Nhà yến", "label": "Nhà yến", "sortOrder": 1 },
+                { "value":"Sơ chế", "label": "Sơ chế", "sortOrder": 2 },
+                { "value":  "Chế biến", "label": "Chế biến", "sortOrder": 3 },
+                { "value": "Đóng gói", "label": "Đóng gói", "sortOrder": 4 },
+               { "value": "Phân phối", "label": "Phân phối", "sortOrder": 5 } ]
+}</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -457,16 +450,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1169,7 +1162,7 @@
         <v>22</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>47</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1228,10 +1221,10 @@
         <v>2</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>16</v>
@@ -1243,7 +1236,7 @@
         <v>22</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1266,10 +1259,10 @@
         <v>2</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>16</v>
@@ -1302,13 +1295,13 @@
         <v>2</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="J14" s="2">
         <v>6</v>
@@ -1338,13 +1331,13 @@
         <v>2</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="J15" s="2">
         <v>7</v>
@@ -1353,7 +1346,7 @@
         <v>22</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1376,10 +1369,10 @@
         <v>2</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>16</v>
@@ -1412,13 +1405,13 @@
         <v>2</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J17" s="2">
         <v>9</v>
@@ -1427,7 +1420,7 @@
         <v>22</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1450,13 +1443,13 @@
         <v>2</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J18" s="2">
         <v>10</v>
@@ -1486,13 +1479,13 @@
         <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J19" s="2">
         <v>11</v>
@@ -1513,22 +1506,22 @@
         <v>1</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F20" s="2">
         <v>3</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J20" s="2">
         <v>1</v>
@@ -1537,7 +1530,7 @@
         <v>23</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1551,22 +1544,22 @@
         <v>1</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F21" s="2">
         <v>3</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J21" s="2">
         <v>2</v>
@@ -1575,7 +1568,7 @@
         <v>23</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1589,22 +1582,22 @@
         <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F22" s="2">
         <v>3</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J22" s="2">
         <v>3</v>
@@ -1613,7 +1606,7 @@
         <v>23</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1627,22 +1620,22 @@
         <v>1</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F23" s="2">
         <v>3</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J23" s="2">
         <v>4</v>
@@ -1651,7 +1644,7 @@
         <v>23</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1665,22 +1658,22 @@
         <v>1</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F24" s="2">
         <v>3</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J24" s="2">
         <v>5</v>
@@ -1689,7 +1682,7 @@
         <v>23</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1703,22 +1696,22 @@
         <v>1</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F25" s="2">
         <v>3</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J25" s="2">
         <v>6</v>
@@ -1727,7 +1720,7 @@
         <v>23</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1741,22 +1734,22 @@
         <v>1</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F26" s="2">
         <v>3</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J26" s="2">
         <v>7</v>
@@ -1765,7 +1758,7 @@
         <v>23</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1779,22 +1772,22 @@
         <v>1</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F27" s="2">
         <v>3</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="J27" s="2">
         <v>8</v>
@@ -1803,7 +1796,7 @@
         <v>23</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1817,22 +1810,22 @@
         <v>1</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F28" s="2">
         <v>4</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J28" s="2">
         <v>1</v>
@@ -1841,7 +1834,7 @@
         <v>23</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1855,22 +1848,22 @@
         <v>1</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F29" s="2">
         <v>4</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J29" s="2">
         <v>2</v>
@@ -1879,7 +1872,7 @@
         <v>23</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1893,22 +1886,22 @@
         <v>1</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F30" s="2">
         <v>4</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J30" s="2">
         <v>3</v>
@@ -1917,7 +1910,7 @@
         <v>23</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -1931,22 +1924,22 @@
         <v>1</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F31" s="2">
         <v>4</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J31" s="2">
         <v>4</v>
@@ -1955,7 +1948,7 @@
         <v>23</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="54" customHeight="1" x14ac:dyDescent="0.25">
@@ -1969,22 +1962,22 @@
         <v>1</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" s="2">
         <v>4</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J32" s="2">
         <v>5</v>
@@ -1993,7 +1986,7 @@
         <v>23</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>

--- a/scripts/tracebility-form-generate.xlsx
+++ b/scripts/tracebility-form-generate.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKING\FREELANCER\YEN\SwifletHome\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11601203-CC5D-44E6-8ACA-F574D5662D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F99B39C-79BA-4571-94DC-C3CFD62EE7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="6" xr2:uid="{EC9FEC76-F761-4AE5-9131-399AA55896AB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="2" activeTab="7" xr2:uid="{EC9FEC76-F761-4AE5-9131-399AA55896AB}"/>
   </bookViews>
   <sheets>
     <sheet name="BRIEF_SWIFT_HOUSE" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="459">
   <si>
     <t>Loại chủ thể</t>
   </si>
@@ -698,13 +698,6 @@
   </si>
   <si>
     <t xml:space="preserve"> {"options": [
-                { "value": "1", "label": "1", "sortOrder": 1 },
-                { "value": "2", "label": "2", "sortOrder": 2 },
-                { "value": "3", "label": "3", "sortOrder": 3 }
-]}</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> {"options": [
                 { "value": "Gỗ", "label": "Gỗ", "sortOrder": 1 },
                 { "value": "Bê tông", "label": "Bê tông", "sortOrder": 2 },
                 { "value": "Đá", "label": "Đá", "sortOrder": 3 },
@@ -857,9 +850,6 @@
     <t>Tên sản phẩm</t>
   </si>
   <si>
-    <t>Phân loại</t>
-  </si>
-  <si>
     <t>Bên giao</t>
   </si>
   <si>
@@ -876,9 +866,6 @@
   </si>
   <si>
     <t>diLotCode</t>
-  </si>
-  <si>
-    <t>diClassification</t>
   </si>
   <si>
     <t>diSender</t>
@@ -1271,9 +1258,6 @@
     <t>Tổng khối lượng</t>
   </si>
   <si>
-    <t>lfpInputProcessings</t>
-  </si>
-  <si>
     <t>lfpProductionDate</t>
   </si>
   <si>
@@ -1563,6 +1547,65 @@
   </si>
   <si>
     <t>rReportAuthority</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {"options": [
+]}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> {"options": [
+                { "value": "Loại 1", "label": "Loại 1", "sortOrder": 1 },
+                { "value": "Loại 2", "label": "Loại 2", "sortOrder": 2 },
+                { "value": "Loại 3", "label": "Loại 3", "sortOrder": 3 }
+]}</t>
+  </si>
+  <si>
+    <t>Số se-ri</t>
+  </si>
+  <si>
+    <t>psSeri</t>
+  </si>
+  <si>
+    <t>{"disabled":true}</t>
+  </si>
+  <si>
+    <t>EXPORT_INFO</t>
+  </si>
+  <si>
+    <t>Metadata hồ sơ xuất</t>
+  </si>
+  <si>
+    <t>Người xuất</t>
+  </si>
+  <si>
+    <t>exporter</t>
+  </si>
+  <si>
+    <t>Ngày giờ xuất</t>
+  </si>
+  <si>
+    <t>exportTime</t>
+  </si>
+  <si>
+    <t>Mã cơ sở</t>
+  </si>
+  <si>
+    <t>facilityCodeExport</t>
+  </si>
+  <si>
+    <t>lfpLotProcessings</t>
+  </si>
+  <si>
+    <t>entireExportFile</t>
+  </si>
+  <si>
+    <t>Hồ sơ xuất</t>
+  </si>
+  <si>
+    <t>file_download</t>
+  </si>
+  <si>
+    <t>{"ext":".pdf"}</t>
   </si>
 </sst>
 </file>
@@ -3839,19 +3882,22 @@
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>187</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>57</v>
+        <v>13</v>
       </c>
       <c r="G2" s="2">
         <v>1</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3865,10 +3911,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>50</v>
@@ -3891,10 +3937,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>50</v>
@@ -3917,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>182</v>
@@ -3943,7 +3989,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>183</v>
@@ -3969,7 +4015,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>184</v>
@@ -3998,7 +4044,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>185</v>
@@ -4013,7 +4059,7 @@
         <v>19</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>189</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="111" customHeight="1" x14ac:dyDescent="0.25">
@@ -4027,7 +4073,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>186</v>
@@ -4042,24 +4088,24 @@
         <v>19</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>203</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>57</v>
@@ -4073,19 +4119,19 @@
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C11" s="2">
         <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>57</v>
@@ -4099,19 +4145,19 @@
     </row>
     <row r="12" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>12</v>
@@ -4125,19 +4171,19 @@
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>57</v>
@@ -4151,19 +4197,19 @@
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C14" s="2">
         <v>2</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>12</v>
@@ -4177,19 +4223,19 @@
     </row>
     <row r="15" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C15" s="2">
         <v>2</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>74</v>
@@ -4206,19 +4252,19 @@
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>74</v>
@@ -4235,19 +4281,19 @@
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="C17" s="2">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>218</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="C17" s="2">
-        <v>3</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>74</v>
@@ -4261,19 +4307,19 @@
     </row>
     <row r="18" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C18" s="2">
         <v>3</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>74</v>
@@ -4287,19 +4333,19 @@
     </row>
     <row r="19" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>74</v>
@@ -4313,19 +4359,19 @@
     </row>
     <row r="20" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>12</v>
@@ -4336,19 +4382,19 @@
     </row>
     <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>12</v>
@@ -4359,19 +4405,19 @@
     </row>
     <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>57</v>
@@ -4382,19 +4428,19 @@
     </row>
     <row r="23" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>13</v>
@@ -4403,7 +4449,7 @@
         <v>137</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4450,7 +4496,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE1FC95-453E-4E43-ADA1-1FA7F1F680C8}">
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.5703125" style="1" customWidth="1"/>
@@ -4497,19 +4543,19 @@
     </row>
     <row r="2" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>42</v>
@@ -4521,59 +4567,57 @@
         <v>137</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>284</v>
-      </c>
+      <c r="I3" s="2"/>
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G4" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>137</v>
@@ -4582,25 +4626,25 @@
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>12</v>
+        <v>109</v>
       </c>
       <c r="G5" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>137</v>
@@ -4609,25 +4653,25 @@
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>109</v>
       </c>
       <c r="G6" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>137</v>
@@ -4636,133 +4680,133 @@
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="2">
+        <v>7</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="2"/>
+    </row>
+    <row r="8" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G7" s="2">
-        <v>6</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="B8" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="I7" s="2"/>
-    </row>
-    <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="2">
-        <v>7</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>57</v>
       </c>
       <c r="G9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>137</v>
       </c>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>57</v>
       </c>
       <c r="G10" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>137</v>
       </c>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C11" s="2">
         <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="G11" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>137</v>
@@ -4771,129 +4815,127 @@
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9" ht="107.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C13" s="2">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G13" s="2">
+        <v>6</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C13" s="2">
-        <v>2</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F13" s="2" t="s">
+    </row>
+    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="2">
-        <v>5</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9" ht="107.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C14" s="2">
-        <v>2</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="G14" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>260</v>
-      </c>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="C15" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="2">
-        <v>7</v>
-      </c>
+      <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="C16" s="2">
-        <v>3</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>12</v>
@@ -4906,19 +4948,19 @@
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C17" s="2">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C17" s="2">
-        <v>3</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>12</v>
@@ -4931,51 +4973,53 @@
     </row>
     <row r="18" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C18" s="2">
         <v>3</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I18" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="19" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>74</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>169</v>
@@ -4983,19 +5027,19 @@
     </row>
     <row r="20" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>74</v>
@@ -5005,24 +5049,24 @@
         <v>155</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>169</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>74</v>
@@ -5036,31 +5080,15 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>74</v>
-      </c>
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>97</v>
-      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
     </row>
     <row r="23" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
@@ -5128,7 +5156,7 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -5139,17 +5167,7 @@
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
     </row>
-    <row r="30" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-    </row>
+    <row r="30" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="32" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5176,7 +5194,6 @@
     <row r="54" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="55" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="56" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -5232,19 +5249,19 @@
     </row>
     <row r="2" spans="1:9" ht="56.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>13</v>
@@ -5256,24 +5273,24 @@
         <v>137</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>42</v>
@@ -5285,24 +5302,24 @@
         <v>137</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>109</v>
@@ -5317,19 +5334,19 @@
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>12</v>
@@ -5344,19 +5361,19 @@
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>57</v>
@@ -5371,19 +5388,19 @@
     </row>
     <row r="7" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>57</v>
@@ -5398,19 +5415,19 @@
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>57</v>
@@ -5425,19 +5442,19 @@
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>74</v>
@@ -5454,17 +5471,17 @@
     </row>
     <row r="10" spans="1:9" ht="216.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2">
         <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>13</v>
@@ -5476,24 +5493,24 @@
         <v>18</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>109</v>
@@ -5508,19 +5525,19 @@
     </row>
     <row r="12" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="C12" s="2">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>109</v>
@@ -5535,16 +5552,16 @@
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>104</v>
@@ -5562,19 +5579,19 @@
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C14" s="2">
         <v>2</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>12</v>
@@ -5589,19 +5606,19 @@
     </row>
     <row r="15" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C15" s="2">
         <v>2</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>57</v>
@@ -5616,19 +5633,19 @@
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C16" s="2">
         <v>2</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>57</v>
@@ -5643,19 +5660,19 @@
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C17" s="2">
         <v>2</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>57</v>
@@ -5670,19 +5687,19 @@
     </row>
     <row r="18" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C18" s="2">
         <v>2</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>12</v>
@@ -5697,19 +5714,19 @@
     </row>
     <row r="19" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C19" s="2">
         <v>2</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>74</v>
@@ -5726,19 +5743,19 @@
     </row>
     <row r="20" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>12</v>
@@ -5753,19 +5770,19 @@
     </row>
     <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>57</v>
@@ -5780,19 +5797,19 @@
     </row>
     <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="C22" s="2">
-        <v>3</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>326</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>57</v>
@@ -5807,19 +5824,19 @@
     </row>
     <row r="23" spans="1:9" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="C23" s="2">
-        <v>3</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>327</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>53</v>
@@ -5831,24 +5848,24 @@
         <v>18</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>109</v>
@@ -5863,19 +5880,19 @@
     </row>
     <row r="25" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C25" s="2">
         <v>3</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>12</v>
@@ -5890,19 +5907,19 @@
     </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C26" s="2">
         <v>3</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>74</v>
@@ -6054,19 +6071,19 @@
     </row>
     <row r="2" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>12</v>
@@ -6080,19 +6097,19 @@
     </row>
     <row r="3" spans="1:9" ht="168.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>13</v>
@@ -6104,24 +6121,24 @@
         <v>137</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>12</v>
@@ -6135,19 +6152,19 @@
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>12</v>
@@ -6161,19 +6178,19 @@
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>57</v>
@@ -6187,19 +6204,19 @@
     </row>
     <row r="7" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>53</v>
@@ -6211,24 +6228,24 @@
         <v>137</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>362</v>
+        <v>454</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>42</v>
@@ -6240,24 +6257,24 @@
         <v>137</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C9" s="2">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>50</v>
@@ -6271,19 +6288,19 @@
     </row>
     <row r="10" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>358</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>50</v>
@@ -6297,19 +6314,19 @@
     </row>
     <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C11" s="2">
         <v>2</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>50</v>
@@ -6323,19 +6340,19 @@
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>57</v>
@@ -6349,19 +6366,19 @@
     </row>
     <row r="13" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>57</v>
@@ -6375,19 +6392,19 @@
     </row>
     <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C14" s="2">
         <v>2</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>12</v>
@@ -6401,19 +6418,19 @@
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C15" s="2">
         <v>3</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>12</v>
@@ -6427,19 +6444,19 @@
     </row>
     <row r="16" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>12</v>
@@ -6453,19 +6470,19 @@
     </row>
     <row r="17" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C17" s="2">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="C17" s="2">
-        <v>3</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>373</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>12</v>
@@ -6479,19 +6496,19 @@
     </row>
     <row r="18" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C18" s="2">
+        <v>3</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C18" s="2">
-        <v>3</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>12</v>
@@ -6505,19 +6522,19 @@
     </row>
     <row r="19" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>12</v>
@@ -6531,19 +6548,19 @@
     </row>
     <row r="20" spans="1:9" ht="117.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>13</v>
@@ -6555,24 +6572,24 @@
         <v>155</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C21" s="2">
         <v>4</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>57</v>
@@ -6586,19 +6603,19 @@
     </row>
     <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C22" s="2">
         <v>4</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>57</v>
@@ -6612,19 +6629,19 @@
     </row>
     <row r="23" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C23" s="2">
         <v>4</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>57</v>
@@ -6638,19 +6655,19 @@
     </row>
     <row r="24" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C24" s="2">
         <v>4</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>12</v>
@@ -6662,7 +6679,35 @@
         <v>137</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C25" s="2">
+        <v>4</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="2">
+        <v>5</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>445</v>
+      </c>
+    </row>
     <row r="26" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="27" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6748,19 +6793,19 @@
     </row>
     <row r="2" spans="1:9" ht="111" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C2" s="2">
         <v>1</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>42</v>
@@ -6772,24 +6817,24 @@
         <v>18</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C3" s="2">
         <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>12</v>
@@ -6804,19 +6849,19 @@
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C4" s="2">
         <v>1</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>12</v>
@@ -6831,19 +6876,19 @@
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>109</v>
@@ -6858,19 +6903,19 @@
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>57</v>
@@ -6885,19 +6930,19 @@
     </row>
     <row r="7" spans="1:9" ht="144.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C7" s="2">
         <v>1</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>53</v>
@@ -6909,24 +6954,24 @@
         <v>18</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2">
@@ -6939,19 +6984,19 @@
     </row>
     <row r="9" spans="1:9" ht="122.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
@@ -6963,24 +7008,24 @@
         <v>18</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="153" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>13</v>
@@ -6992,24 +7037,24 @@
         <v>18</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="C11" s="2">
-        <v>2</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>411</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>30</v>
@@ -7024,16 +7069,16 @@
     </row>
     <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>167</v>
@@ -7053,19 +7098,19 @@
     </row>
     <row r="13" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C13" s="2">
         <v>2</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>12</v>
@@ -7080,19 +7125,19 @@
     </row>
     <row r="14" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C14" s="2">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="C14" s="2">
-        <v>2</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>109</v>
@@ -7107,19 +7152,19 @@
     </row>
     <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C15" s="2">
         <v>2</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>12</v>
@@ -7136,19 +7181,19 @@
     </row>
     <row r="16" spans="1:9" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C16" s="2">
-        <v>3</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>436</v>
-      </c>
       <c r="E16" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>42</v>
@@ -7160,24 +7205,24 @@
         <v>19</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="135" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>13</v>
@@ -7189,24 +7234,24 @@
         <v>19</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C18" s="2">
         <v>3</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>109</v>
@@ -7221,19 +7266,19 @@
     </row>
     <row r="19" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C19" s="2">
         <v>3</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>12</v>
@@ -7248,19 +7293,19 @@
     </row>
     <row r="20" spans="1:9" ht="111" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>13</v>
@@ -7272,24 +7317,24 @@
         <v>19</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>57</v>
@@ -7304,19 +7349,19 @@
     </row>
     <row r="22" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C22" s="2">
         <v>3</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>57</v>
@@ -7331,19 +7376,19 @@
     </row>
     <row r="23" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C23" s="2">
         <v>3</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>12</v>
@@ -7358,19 +7403,19 @@
     </row>
     <row r="24" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C24" s="2">
         <v>3</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>74</v>
@@ -7497,7 +7542,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE6E2B34-98F0-4651-8803-FF98EE6C84D6}">
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="1" customWidth="1"/>
@@ -7505,7 +7550,7 @@
     <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.28515625" style="1" customWidth="1"/>
     <col min="5" max="5" width="30.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19" style="1" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" style="1" customWidth="1"/>
     <col min="9" max="9" width="64" style="1" customWidth="1"/>
@@ -7543,48 +7588,120 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="111" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
+      <c r="A3" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="2">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="G5" s="2">
+        <v>4</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
@@ -7619,7 +7736,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -7630,7 +7747,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -7641,7 +7758,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -7652,7 +7769,7 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="1:9" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -7674,7 +7791,7 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -7685,7 +7802,7 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:9" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -7789,7 +7906,7 @@
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="E24" s="5"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
@@ -7800,7 +7917,7 @@
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
-      <c r="E25" s="5"/>
+      <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
@@ -7861,7 +7978,7 @@
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
     </row>
-    <row r="31" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -7872,17 +7989,7 @@
       <c r="H31" s="2"/>
       <c r="I31" s="2"/>
     </row>
-    <row r="32" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-    </row>
+    <row r="32" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7909,7 +8016,6 @@
     <row r="56" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
